--- a/artfynd/A 14968-2026 artfynd.xlsx
+++ b/artfynd/A 14968-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98547088</v>
+        <v>128226057</v>
       </c>
       <c r="B2" t="n">
-        <v>57435</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100077</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åssjöälven/Halgån, Vrm</t>
+          <t>Länsmansflån, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413428.435511261</v>
+        <v>413475</v>
       </c>
       <c r="R2" t="n">
-        <v>6710482.420710168</v>
+        <v>6710151</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-02-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-02-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Axel Magnusson</t>
+          <t>Agnes Rengren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Axel Magnusson</t>
+          <t>Agnes Rengren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128226055</v>
+        <v>128226040</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>78730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413476</v>
+        <v>413318</v>
       </c>
       <c r="R3" t="n">
-        <v>6710152</v>
+        <v>6709989</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128226057</v>
+        <v>128226054</v>
       </c>
       <c r="B4" t="n">
-        <v>80226</v>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413475</v>
+        <v>413365</v>
       </c>
       <c r="R4" t="n">
-        <v>6710151</v>
+        <v>6710035</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,6 +963,733 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112083497</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Åssjöälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>413472</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6710139</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonas Göransson, Olavi Niemelä</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128226055</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Länsmansflån, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>413476</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6710152</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128226056</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Länsmansflån, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>413480</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6710151</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128226058</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Länsmansflån, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>413479</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6710150</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>16878866</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Västra Åssjön, Dala-gränsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>413430</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6710488</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-09-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-09-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Vattendrag</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Bro, grusväg, vattendrag 2-5 m brett, block, sten, grus, sand, blandskog.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Ericsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Therese Ericsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Övervakning av utter i Värmlands län - barmarksinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>98547088</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Åssjöälven/Halgån, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>413428</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6710482</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-02-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-02-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars-Axel Magnusson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars-Axel Magnusson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112083503</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Åssjöälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>413472</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6710139</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jonas Göransson, Olavi Niemelä</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14968-2026 artfynd.xlsx
+++ b/artfynd/A 14968-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128226057</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128226040</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128226054</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083497</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128226055</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128226056</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128226058</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
           <t>Övervakning av utter i Värmlands län - barmarksinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16878866</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98547088</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1690,8 +1740,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083503</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>